--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486258_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486258_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7752</v>
+        <v>8.226000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4575</v>
+        <v>4.5693</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3177</v>
+        <v>3.6567</v>
       </c>
       <c r="G2" t="n">
         <v>4.3349</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1575</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1526</v>
+        <v>0.2644</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0049</v>
+        <v>0.344</v>
       </c>
       <c r="V2" t="n">
         <v>1.3252</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0007</v>
+        <v>4.5104</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4218</v>
+        <v>2.9315</v>
       </c>
       <c r="F3" t="n">
         <v>1.5789</v>
@@ -688,10 +688,10 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>1.007</v>
+        <v>0.5167</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6802</v>
+        <v>0.1899</v>
       </c>
       <c r="U3" t="n">
         <v>0.3268</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>U. MENDICOTE RUBIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2277</v>
+        <v>2.5444</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1476</v>
+        <v>1.5438</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0801</v>
+        <v>1.0006</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0342</v>
+        <v>2.7166</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7275</v>
+        <v>2.6035</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6933</v>
+        <v>0.1131</v>
       </c>
       <c r="J4" t="n">
-        <v>1.021</v>
+        <v>2.8753</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5417</v>
+        <v>2.7223</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5627</v>
+        <v>0.153</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0552</v>
+        <v>-0.1587</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1858</v>
+        <v>-0.1188</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8694</v>
+        <v>-0.0399</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7229</v>
+        <v>0.3758</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1717</v>
+        <v>-0.2439</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5512</v>
+        <v>0.6198</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7565</v>
+        <v>-0.113</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5034</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>U. MENDICOTE RUBIO</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4134</v>
+        <v>2.1564</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3203</v>
+        <v>2.477</v>
       </c>
       <c r="F5" t="n">
-        <v>1.093</v>
+        <v>-0.3206</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7166</v>
+        <v>-0.0342</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6035</v>
+        <v>-1.7275</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1131</v>
+        <v>1.6933</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8753</v>
+        <v>1.021</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7223</v>
+        <v>-1.5417</v>
       </c>
       <c r="L5" t="n">
-        <v>0.153</v>
+        <v>2.5627</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1587</v>
+        <v>-1.0552</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1188</v>
+        <v>-0.1858</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0399</v>
+        <v>-0.8694</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2448</v>
+        <v>0.6516</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4675</v>
+        <v>0.5011</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.1505</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.113</v>
+        <v>1.7565</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.113</v>
+        <v>-0.5034</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5917</v>
+        <v>1.8336</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1438</v>
+        <v>1.3241</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4479</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>1.1701</v>
@@ -922,13 +922,13 @@
         <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1884</v>
+        <v>0.0535</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0156</v>
+        <v>0.1959</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2041</v>
+        <v>-0.1424</v>
       </c>
       <c r="V6" t="n">
         <v>-1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5233</v>
+        <v>0.5109</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3431</v>
+        <v>1.2998</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8198</v>
+        <v>-0.7889</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1103</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6884</v>
+        <v>-0.7009</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0769</v>
+        <v>-0.1202</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6116</v>
+        <v>-0.5807</v>
       </c>
       <c r="V7" t="n">
         <v>1.017</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4011</v>
+        <v>0.1991</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9282</v>
+        <v>-0.6362</v>
       </c>
       <c r="F8" t="n">
-        <v>0.527</v>
+        <v>0.8353</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4419</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.721</v>
+        <v>-0.1208</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6165</v>
+        <v>-0.3245</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1046</v>
+        <v>0.2037</v>
       </c>
       <c r="V8" t="n">
         <v>0.5443</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5411</v>
+        <v>-0.5527</v>
       </c>
       <c r="E9" t="n">
-        <v>0.292</v>
+        <v>0.4038</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8331</v>
+        <v>-0.9564</v>
       </c>
       <c r="G9" t="n">
         <v>0.3971</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1918</v>
+        <v>0.1803</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0565</v>
+        <v>0.0553</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2483</v>
+        <v>0.125</v>
       </c>
       <c r="V9" t="n">
         <v>-1.13</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8234</v>
+        <v>-1.3386</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4984</v>
+        <v>1.0139</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3217</v>
+        <v>-2.3526</v>
       </c>
       <c r="G10" t="n">
         <v>-0.07099999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2691</v>
+        <v>-0.7844</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8784</v>
+        <v>-0.3629</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3907</v>
+        <v>-0.4215</v>
       </c>
       <c r="V10" t="n">
         <v>0.8218</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4819</v>
+        <v>-3.4627</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8774</v>
+        <v>-2.7656</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6046</v>
+        <v>-0.697</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6992</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2347</v>
+        <v>-0.2154</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1763</v>
+        <v>0.0838</v>
       </c>
       <c r="V11" t="n">
         <v>-0.678</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.2845</v>
+        <v>14.6268</v>
       </c>
       <c r="E12" t="n">
-        <v>11.8189</v>
+        <v>12.1614</v>
       </c>
       <c r="F12" t="n">
-        <v>2.465399999999999</v>
+        <v>2.465599999999999</v>
       </c>
       <c r="G12" t="n">
         <v>9.040400000000002</v>
@@ -1390,13 +1390,13 @@
         <v>13.0503</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2224000000000001</v>
+        <v>0.5648000000000004</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4867000000000001</v>
+        <v>-0.1441</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7086999999999998</v>
+        <v>0.709</v>
       </c>
       <c r="V12" t="n">
         <v>3.934200000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6199</v>
+        <v>3.9263</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9779</v>
+        <v>3.5309</v>
       </c>
       <c r="F13" t="n">
-        <v>0.642</v>
+        <v>0.3954</v>
       </c>
       <c r="G13" t="n">
         <v>1.0475</v>
@@ -1468,13 +1468,13 @@
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9422</v>
+        <v>1.2486</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1596</v>
+        <v>0.7126</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7825</v>
+        <v>0.536</v>
       </c>
       <c r="V13" t="n">
         <v>0.7602</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0522</v>
+        <v>-0.0339</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8656</v>
+        <v>0.7538</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8134</v>
+        <v>-0.7877</v>
       </c>
       <c r="G14" t="n">
         <v>-0.7069</v>
@@ -1546,13 +1546,13 @@
         <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8683</v>
+        <v>0.7823</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4062</v>
+        <v>0.2944</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4622</v>
+        <v>0.4879</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5443</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6784</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1005</v>
+        <v>0.0113</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5779</v>
+        <v>-0.5471</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5620000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1164</v>
+        <v>0.0261</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>G. KALSCHEUR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.5786</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2344</v>
+        <v>0.9305</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2027</v>
+        <v>-1.509</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4134</v>
+        <v>0.6005</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9251</v>
+        <v>2.2293</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5117</v>
+        <v>-1.6288</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6849</v>
+        <v>2.9657</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9942</v>
+        <v>3.1936</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6791</v>
+        <v>-0.2279</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0983</v>
+        <v>-2.3652</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.9643</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1674</v>
+        <v>-1.4009</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.435</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.305</v>
+        <v>-2.6101</v>
       </c>
       <c r="R16" t="n">
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1198</v>
+        <v>-0.569</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1454</v>
+        <v>-0.5552</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0256</v>
+        <v>-0.0138</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. KALSCHEUR</t>
+          <t>C. JÜRGENS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0012</v>
+        <v>-0.6744</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5952</v>
+        <v>-0.5831</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5964</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6005</v>
+        <v>-1.4599</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2293</v>
+        <v>1.1011</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6288</v>
+        <v>-2.5611</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9657</v>
+        <v>-0.8717</v>
       </c>
       <c r="K17" t="n">
-        <v>3.1936</v>
+        <v>1.287</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2279</v>
+        <v>-2.1587</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3652</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9643</v>
+        <v>-0.1858</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4009</v>
+        <v>-0.4024</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.6101</v>
+        <v>-0.2175</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9916</v>
+        <v>0.4359</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8904</v>
+        <v>-0.0589</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1012</v>
+        <v>0.4948</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>-0.9554</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. JÜRGENS</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1035</v>
+        <v>-0.7977</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8066</v>
+        <v>-0.7248</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2969</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4599</v>
+        <v>0.4132</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1011</v>
+        <v>-0.6538</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.5611</v>
+        <v>1.067</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8717</v>
+        <v>1.0189</v>
       </c>
       <c r="K18" t="n">
-        <v>1.287</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.1587</v>
+        <v>1.7029</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.6057</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1858</v>
+        <v>0.0302</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4024</v>
+        <v>-0.6359</v>
       </c>
       <c r="P18" t="n">
-        <v>1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2175</v>
+        <v>-2.6101</v>
       </c>
       <c r="R18" t="n">
         <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0068</v>
+        <v>0.6162</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2824</v>
+        <v>0.4759</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2892</v>
+        <v>0.1403</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9554</v>
+        <v>-0.7395</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.3904</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5204</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2539</v>
+        <v>-1.1429</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0308</v>
+        <v>-1.121</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2847</v>
+        <v>-0.0219</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0798</v>
+        <v>-2.6873</v>
       </c>
       <c r="H19" t="n">
-        <v>0.742</v>
+        <v>0.2706</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6622</v>
+        <v>-2.9579</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9142</v>
+        <v>-0.8536</v>
       </c>
       <c r="K19" t="n">
-        <v>0.876</v>
+        <v>0.7879</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0382</v>
+        <v>-1.6415</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8344</v>
+        <v>-1.8337</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1339</v>
+        <v>-0.5173</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7004</v>
+        <v>-1.3164</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>0.209</v>
+        <v>0.0442</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3341</v>
+        <v>-0.0276</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1251</v>
+        <v>0.0718</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3252</v>
+        <v>0.1952</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4618</v>
+        <v>-1.3228</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0601</v>
+        <v>-0.2126</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4017</v>
+        <v>-1.1102</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4132</v>
+        <v>-0.4134</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6538</v>
+        <v>-1.9251</v>
       </c>
       <c r="I20" t="n">
-        <v>1.067</v>
+        <v>1.5117</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0189</v>
+        <v>1.6849</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.9942</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7029</v>
+        <v>2.6791</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6057</v>
+        <v>-2.0983</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0302</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6359</v>
+        <v>-1.1674</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.6101</v>
+        <v>-1.305</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0479</v>
+        <v>-0.4744</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1406</v>
+        <v>-0.5924</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1886</v>
+        <v>0.1181</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7516</v>
+        <v>-1.5827</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2156</v>
+        <v>0.5838</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5361</v>
+        <v>-2.1665</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.033</v>
+        <v>0.0798</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7031</v>
+        <v>0.742</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3299</v>
+        <v>-0.6622</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5977</v>
+        <v>0.9142</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2862</v>
+        <v>0.876</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6885</v>
+        <v>0.0382</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4353</v>
+        <v>-0.8344</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4169</v>
+        <v>-0.1339</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0184</v>
+        <v>-0.7004</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.519</v>
+        <v>-0.1199</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5997</v>
+        <v>-0.113</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0806</v>
+        <v>-0.0069</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3252</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8408</v>
+        <v>-1.6481</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4638</v>
+        <v>-1.2403</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.377</v>
+        <v>-0.4078</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1063</v>
@@ -2170,13 +2170,13 @@
         <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0479</v>
+        <v>0.2406</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.125</v>
+        <v>0.0985</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1729</v>
+        <v>0.1421</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2283</v>
+        <v>-2.4157</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9033</v>
+        <v>-0.9979</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.325</v>
+        <v>-1.4179</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6873</v>
+        <v>-2.033</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2706</v>
+        <v>-1.7031</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9579</v>
+        <v>-0.3299</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8536</v>
+        <v>-0.5977</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7879</v>
+        <v>-1.2862</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.6415</v>
+        <v>0.6885</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8337</v>
+        <v>-1.4353</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5173</v>
+        <v>-0.4169</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3164</v>
+        <v>-1.0184</v>
       </c>
       <c r="P23" t="n">
+        <v>1.0875</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.2175</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.305</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-0.435</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.7401</v>
-      </c>
       <c r="S23" t="n">
-        <v>-1.0413</v>
+        <v>-0.1451</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8099</v>
+        <v>-0.1826</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2313</v>
+        <v>0.0375</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1952</v>
+        <v>-1.3252</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.6686</v>
+        <v>-5.9878</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6194</v>
+        <v>-3.3959</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0492</v>
+        <v>-2.592</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2125</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4985</v>
+        <v>-0.8178</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9589</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5396</v>
+        <v>-0.0823</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2359,28 +2359,28 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.2842</v>
+        <v>-12.7941</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.465400000000002</v>
+        <v>-2.4653</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.819</v>
+        <v>-10.3289</v>
       </c>
       <c r="G25" t="n">
-        <v>-9.0403</v>
+        <v>-9.040299999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0002000000000000335</v>
+        <v>-0.0002000000000006441</v>
       </c>
       <c r="I25" t="n">
         <v>-9.0403</v>
       </c>
       <c r="J25" t="n">
-        <v>7.472100000000001</v>
+        <v>7.472099999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>5.583399999999999</v>
+        <v>5.5834</v>
       </c>
       <c r="L25" t="n">
         <v>1.8887</v>
@@ -2404,16 +2404,16 @@
         <v>11.9627</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2223000000000004</v>
+        <v>1.2677</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7088000000000001</v>
+        <v>-0.7089</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4865</v>
+        <v>1.9769</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.934200000000001</v>
+        <v>-3.9342</v>
       </c>
       <c r="W25" t="n">
         <v>3.8217</v>
